--- a/grupos/3ALCV - Estadisticos 20211.xlsx
+++ b/grupos/3ALCV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -182,10 +182,10 @@
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Rivera Serra Alma Lilian</t>
@@ -947,19 +947,19 @@
         <v>-1</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -983,19 +983,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>6</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -1009,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -1024,19 +1024,19 @@
         <v>-1</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1060,10 +1060,10 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -1101,19 +1101,19 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1187,7 +1187,7 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1264,7 +1264,7 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1300,7 +1300,7 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1341,7 +1341,7 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1409,19 +1409,19 @@
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1448,7 +1448,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1495,7 +1495,7 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1572,7 +1572,7 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1640,16 +1640,16 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1685,7 +1685,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1717,22 +1717,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1753,7 +1753,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>9</v>
@@ -1794,16 +1794,16 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1874,19 +1874,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1910,16 +1910,16 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1948,22 +1948,22 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1990,16 +1990,16 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2025,19 +2025,19 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2064,13 +2064,13 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2102,22 +2102,22 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2147,10 +2147,10 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2179,22 +2179,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2215,19 +2215,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>9</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2265,7 +2265,7 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2301,7 +2301,7 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>-1</v>
@@ -2333,22 +2333,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2381,7 +2381,7 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2419,7 +2419,7 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2487,22 +2487,22 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2523,7 +2523,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2532,10 +2532,10 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2564,22 +2564,22 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2609,10 +2609,10 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2641,19 +2641,19 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2680,7 +2680,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2718,22 +2718,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2780,7 +2780,7 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -2795,16 +2795,16 @@
         <v>-1</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2831,16 +2831,16 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2872,22 +2872,22 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2920,10 +2920,10 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2952,13 +2952,13 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -2988,13 +2988,13 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>8</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3029,19 +3029,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3065,7 +3065,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -3077,7 +3077,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3106,13 +3106,13 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3183,19 +3183,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3257,22 +3257,22 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3296,7 +3296,7 @@
         <v>9</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -3305,7 +3305,7 @@
         <v>10</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I2">
         <v>11</v>
@@ -3405,19 +3405,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>67.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="G3">
-        <v>32.26</v>
+        <v>25.81</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3437,19 +3437,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>70.97</v>
+        <v>74.19</v>
       </c>
       <c r="G4">
-        <v>29.03</v>
+        <v>25.81</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -3472,27 +3472,27 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>77.42</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="H5">
         <v>8</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>22.58</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3501,25 +3501,25 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>77.42</v>
+        <v>83.87</v>
       </c>
       <c r="G6">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>9.68</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3561,7 +3561,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3602,24 +3602,24 @@
         <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>20330051920191</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3630,16 +3630,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920191</v>
+        <v>20330051920193</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -3650,22 +3650,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920193</v>
+        <v>20330051920392</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3682,24 +3682,24 @@
         <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920392</v>
+        <v>20330051920194</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3710,16 +3710,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920194</v>
+        <v>20330051920202</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -3730,22 +3730,22 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920202</v>
+        <v>20330051920203</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3762,30 +3762,30 @@
         <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920203</v>
+        <v>20330051920204</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3802,7 +3802,7 @@
         <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
@@ -3822,30 +3822,30 @@
         <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920204</v>
+        <v>20330051920205</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3862,7 +3862,7 @@
         <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>54</v>
@@ -3882,30 +3882,30 @@
         <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920205</v>
+        <v>20330051920207</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3922,7 +3922,7 @@
         <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>54</v>
@@ -3942,69 +3942,29 @@
         <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920207</v>
+        <v>20330051920213</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920213</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920213</v>
-      </c>
-      <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4092,16 +4052,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920190</v>
+        <v>20330051920392</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4109,16 +4069,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920392</v>
+        <v>20330051920203</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4126,50 +4086,50 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920203</v>
+        <v>20330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920213</v>
+        <v>20330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920191</v>
+        <v>20330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4177,16 +4137,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920193</v>
+        <v>20330051920194</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4194,16 +4154,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920194</v>
+        <v>20330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4211,16 +4171,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920202</v>
+        <v>20330051920213</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4573,7 +4533,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4605,22 +4565,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920177</v>
+        <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4628,62 +4588,62 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920177</v>
+        <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920191</v>
+        <v>20330051920213</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920202</v>
+        <v>20330051920213</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4692,6 +4652,98 @@
         <v>52</v>
       </c>
       <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920177</v>
+      </c>
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920177</v>
+      </c>
+      <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920191</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920202</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20211.xlsx
+++ b/grupos/3ALCV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -1181,7 +1181,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1217,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1240,7 +1240,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1258,7 +1258,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1294,7 +1294,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1335,7 +1335,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1371,7 +1371,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1471,7 +1471,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1489,7 +1489,7 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1566,7 +1566,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1602,7 +1602,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -2241,7 +2241,7 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -2259,7 +2259,7 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2295,7 +2295,7 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2395,7 +2395,7 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -2413,7 +2413,7 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2449,7 +2449,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -3501,25 +3501,25 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="G6">
+        <v>19.35</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>83.87</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>16.13</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3561,7 +3561,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3662,24 +3662,24 @@
         <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920392</v>
+        <v>20330051920194</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -3690,16 +3690,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920194</v>
+        <v>20330051920202</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3710,16 +3710,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920202</v>
+        <v>20330051920203</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -3730,36 +3730,36 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920203</v>
+        <v>20330051920204</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920203</v>
+        <v>20330051920204</v>
       </c>
       <c r="B10" t="s">
         <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -3770,201 +3770,101 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920204</v>
+        <v>20330051920205</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920204</v>
+        <v>20330051920205</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920204</v>
+        <v>20330051920207</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920205</v>
+        <v>20330051920207</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920205</v>
+        <v>20330051920213</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920205</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920207</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920207</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920207</v>
-      </c>
-      <c r="B19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920213</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4013,7 +3913,7 @@
         <v>88</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4030,7 +3930,7 @@
         <v>89</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4047,55 +3947,55 @@
         <v>90</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920392</v>
+        <v>20330051920190</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920203</v>
+        <v>20330051920191</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920190</v>
+        <v>20330051920193</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4103,16 +4003,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920191</v>
+        <v>20330051920392</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4120,16 +4020,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920193</v>
+        <v>20330051920194</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4137,16 +4037,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920194</v>
+        <v>20330051920202</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4154,16 +4054,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920202</v>
+        <v>20330051920203</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11">
         <v>1</v>

--- a/grupos/3ALCV - Estadisticos 20211.xlsx
+++ b/grupos/3ALCV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,15 +179,15 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -209,6 +209,9 @@
     <t>ARIAS</t>
   </si>
   <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -218,6 +221,24 @@
     <t>CHICO</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ESPERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -227,19 +248,46 @@
     <t>LUIS</t>
   </si>
   <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>GOMEZ</t>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>REYES</t>
@@ -248,6 +296,24 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
@@ -260,15 +326,42 @@
     <t>DAMIEN</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
     <t>REYNA ARISBETH</t>
   </si>
   <si>
     <t>ANALI</t>
   </si>
   <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
     <t>DULCE FERNANDA</t>
   </si>
   <si>
@@ -278,6 +371,27 @@
     <t>KITZIA YAMILET</t>
   </si>
   <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MILAGROS</t>
+  </si>
+  <si>
     <t>ITZEL</t>
   </si>
   <si>
@@ -290,142 +404,28 @@
     <t>CLARET YAZMIN</t>
   </si>
   <si>
+    <t>MARITZA JULIANA</t>
+  </si>
+  <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>YEILI DAYNERIS</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>DIANA SARAY</t>
+  </si>
+  <si>
+    <t>INGRID SARAI</t>
+  </si>
+  <si>
     <t>SUSANA</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
-    <t>MARITZA JULIANA</t>
-  </si>
-  <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>YEILI DAYNERIS</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>DIANA SARAY</t>
-  </si>
-  <si>
-    <t>INGRID SARAI</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
@@ -944,7 +944,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -962,25 +962,25 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -992,13 +992,13 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1021,7 +1021,7 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>8</v>
@@ -1039,43 +1039,43 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>7</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>7</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1116,25 +1116,25 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1175,61 +1175,61 @@
         <v>6</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>5</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1252,61 +1252,61 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>5</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1329,61 +1329,61 @@
         <v>5</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>5</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1406,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>8</v>
@@ -1424,25 +1424,25 @@
         <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1454,13 +1454,13 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1483,61 +1483,61 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>5</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>6</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1557,64 +1557,64 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>5</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1652,43 +1652,43 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>7</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1735,22 +1735,22 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1762,13 +1762,13 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1806,28 +1806,28 @@
         <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1839,10 +1839,10 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1871,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>9</v>
@@ -1889,22 +1889,22 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1922,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1966,34 +1966,34 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>7</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -2040,40 +2040,40 @@
         <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>8</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>8</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2120,34 +2120,34 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2197,22 +2197,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2250,64 +2250,64 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2351,22 +2351,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2378,7 +2378,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2404,64 +2404,64 @@
         <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>5</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2505,22 +2505,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2582,22 +2582,22 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2609,13 +2609,13 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2656,31 +2656,31 @@
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>8</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2736,22 +2736,22 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2763,7 +2763,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2792,7 +2792,7 @@
         <v>5</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>7</v>
@@ -2807,28 +2807,28 @@
         <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>6</v>
@@ -2843,10 +2843,10 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2890,22 +2890,22 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2949,58 +2949,58 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T30">
         <v>7</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>7</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3026,46 +3026,46 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T31">
         <v>8</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -3074,10 +3074,10 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3103,58 +3103,58 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>9</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3180,7 +3180,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>8</v>
@@ -3198,22 +3198,22 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3225,7 +3225,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3275,34 +3275,34 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>9</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>9</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3376,27 +3376,27 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>64.52</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>35.48</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -3405,16 +3405,16 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>74.19</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G3">
-        <v>25.81</v>
+        <v>19.35</v>
       </c>
       <c r="H3">
         <v>7.4</v>
@@ -3428,28 +3428,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>31</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>74.19</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>25.81</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3460,39 +3460,39 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>31</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>77.42</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3501,19 +3501,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>19.35</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3561,7 +3561,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3586,286 +3586,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920190</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920191</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920193</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920392</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920194</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920202</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920203</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920204</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920204</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920205</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920205</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920207</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920207</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920213</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3901,200 +3621,200 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920204</v>
+        <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920205</v>
+        <v>20330051920191</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920207</v>
+        <v>20330051920192</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920190</v>
+        <v>20330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
         <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920191</v>
+        <v>20330051920392</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920193</v>
+        <v>20330051920194</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920392</v>
+        <v>20330051920196</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920194</v>
+        <v>20330051920197</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920202</v>
+        <v>20330051920198</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920203</v>
+        <v>20330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920213</v>
+        <v>20330051920200</v>
       </c>
       <c r="B12" t="s">
         <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920192</v>
+        <v>20330051920201</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>122</v>
@@ -4105,13 +3825,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920196</v>
+        <v>19330051920280</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
         <v>123</v>
@@ -4122,13 +3842,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920197</v>
+        <v>20330051920202</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
         <v>124</v>
@@ -4139,13 +3859,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920198</v>
+        <v>20330051920203</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
         <v>125</v>
@@ -4156,13 +3876,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920199</v>
+        <v>20330051920204</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
         <v>126</v>
@@ -4173,13 +3893,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920200</v>
+        <v>20330051920205</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
         <v>127</v>
@@ -4190,13 +3910,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920201</v>
+        <v>20330051920206</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>128</v>
@@ -4207,13 +3927,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920280</v>
+        <v>20330051920207</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
         <v>129</v>
@@ -4224,13 +3944,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920206</v>
+        <v>20330051920208</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
         <v>130</v>
@@ -4241,13 +3961,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920208</v>
+        <v>20330051920209</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
         <v>131</v>
@@ -4258,13 +3978,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920209</v>
+        <v>20330051920210</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
         <v>132</v>
@@ -4275,13 +3995,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920210</v>
+        <v>20330051920211</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
         <v>133</v>
@@ -4292,13 +4012,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920211</v>
+        <v>20330051920212</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
         <v>134</v>
@@ -4309,13 +4029,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920212</v>
+        <v>20330051920213</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
         <v>135</v>
@@ -4329,10 +4049,10 @@
         <v>20330051920214</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>136</v>
@@ -4346,10 +4066,10 @@
         <v>20330051920215</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
         <v>137</v>
@@ -4363,10 +4083,10 @@
         <v>19330051920177</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
         <v>138</v>
@@ -4380,10 +4100,10 @@
         <v>20330051920217</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
         <v>139</v>
@@ -4397,10 +4117,10 @@
         <v>20330051920218</v>
       </c>
       <c r="B31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" t="s">
         <v>105</v>
-      </c>
-      <c r="C31" t="s">
-        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>140</v>
@@ -4414,10 +4134,10 @@
         <v>20330051920219</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
         <v>141</v>
@@ -4433,7 +4153,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4465,22 +4185,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920190</v>
+        <v>20330051920193</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
         <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4488,16 +4208,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>20330051920193</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
         <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4506,27 +4226,27 @@
         <v>52</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920213</v>
+        <v>20330051920392</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4534,16 +4254,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920213</v>
+        <v>20330051920392</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4552,24 +4272,24 @@
         <v>52</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920177</v>
+        <v>20330051920194</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
@@ -4580,22 +4300,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920177</v>
+        <v>20330051920194</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4603,39 +4323,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920191</v>
+        <v>20330051920203</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920202</v>
+        <v>20330051920203</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4644,7 +4364,214 @@
         <v>52</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920204</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920204</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920207</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920207</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920205</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920214</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920215</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920177</v>
+      </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
